--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.52570371783902</v>
+        <v>7.560426854148841</v>
       </c>
       <c r="D2" t="n">
-        <v>46.41148185247222</v>
+        <v>7.541865801026736</v>
       </c>
       <c r="E2" t="n">
-        <v>8.917654024298164</v>
+        <v>1.449118778948452</v>
       </c>
       <c r="F2" t="n">
-        <v>8.809289580627679</v>
+        <v>1.431509556851998</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.44819693984774</v>
+        <v>3.485332002725257</v>
       </c>
       <c r="D3" t="n">
-        <v>21.60911346834649</v>
+        <v>3.511480938606305</v>
       </c>
       <c r="E3" t="n">
-        <v>8.917654024298164</v>
+        <v>1.449118778948452</v>
       </c>
       <c r="F3" t="n">
-        <v>8.809289580627679</v>
+        <v>1.431509556851998</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.50285285874077</v>
+        <v>5.769213589545375</v>
       </c>
       <c r="D4" t="n">
-        <v>35.55056692983942</v>
+        <v>5.776967126098906</v>
       </c>
       <c r="E4" t="n">
-        <v>8.917654024298164</v>
+        <v>1.449118778948452</v>
       </c>
       <c r="F4" t="n">
-        <v>8.809289580627679</v>
+        <v>1.431509556851998</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.17572632186219</v>
+        <v>5.878555527302606</v>
       </c>
       <c r="D5" t="n">
-        <v>35.81676538238609</v>
+        <v>5.820224374637741</v>
       </c>
       <c r="E5" t="n">
-        <v>8.917654024298164</v>
+        <v>1.449118778948452</v>
       </c>
       <c r="F5" t="n">
-        <v>8.809289580627679</v>
+        <v>1.431509556851998</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
